--- a/data/analysis/pypsa_eur_data.xlsx
+++ b/data/analysis/pypsa_eur_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakeri\My Drive\Job\IIASA\Projects\ECEMF\WP1\Storage survey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakeri\My Drive\Job\IIASA\Projects\ECEMF\WP1\Storage survey\storage-iam-paper\data\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBB49EB-AB8C-4048-A7F9-8954CE7C05FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5663DC03-B692-4E6C-B9BD-2EB278AAA691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{8B1BFF7F-92A3-442A-ACAF-EB4D6B28BEC1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" activeTab="1" xr2:uid="{8B1BFF7F-92A3-442A-ACAF-EB4D6B28BEC1}"/>
   </bookViews>
   <sheets>
     <sheet name="pypsa" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="52">
   <si>
     <t>tech</t>
   </si>
@@ -177,9 +177,6 @@
     <t xml:space="preserve">Electricity storage to peak demand </t>
   </si>
   <si>
-    <t>Share of VRE from total generation</t>
-  </si>
-  <si>
     <t>Share of VRE from total capacity</t>
   </si>
   <si>
@@ -187,6 +184,12 @@
   </si>
   <si>
     <t>Total VRE electricity generation (TWh)</t>
+  </si>
+  <si>
+    <t>Share of VRE in total generation</t>
+  </si>
+  <si>
+    <t>Share of solar in total generation</t>
   </si>
 </sst>
 </file>
@@ -723,7 +726,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
@@ -757,6 +760,7 @@
     <xf numFmtId="1" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="34" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1133,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47188B1-59EF-4F82-9329-8DF67330DDB8}">
-  <dimension ref="A1:BK51"/>
+  <dimension ref="A1:BK52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
@@ -9153,7 +9157,7 @@
     </row>
     <row r="44" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" s="9">
         <f>B38/B37</f>
@@ -9850,7 +9854,7 @@
     </row>
     <row r="49" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="24">
         <v>9938.3499766566183</v>
@@ -10041,7 +10045,7 @@
     </row>
     <row r="50" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="24">
         <v>9245.0636553404911</v>
@@ -10232,7 +10236,7 @@
     </row>
     <row r="51" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B51" s="25">
         <f>B50/B49</f>
@@ -10481,6 +10485,259 @@
       <c r="BK51" s="25">
         <f t="shared" si="8"/>
         <v>0.92546840378826012</v>
+      </c>
+    </row>
+    <row r="52" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="33">
+        <f>B13/B49</f>
+        <v>0.30247475758659975</v>
+      </c>
+      <c r="C52" s="33">
+        <f t="shared" ref="C52:BK52" si="9">C13/C49</f>
+        <v>0.31419265988316142</v>
+      </c>
+      <c r="D52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29637135812537235</v>
+      </c>
+      <c r="E52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.3522500828095686</v>
+      </c>
+      <c r="F52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.33545957046009806</v>
+      </c>
+      <c r="G52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.27386041266813199</v>
+      </c>
+      <c r="H52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.28887895912508049</v>
+      </c>
+      <c r="I52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29417107346623494</v>
+      </c>
+      <c r="J52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.34652767326970918</v>
+      </c>
+      <c r="K52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.32849326305280996</v>
+      </c>
+      <c r="L52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.2871079658144936</v>
+      </c>
+      <c r="M52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.34421622666282736</v>
+      </c>
+      <c r="N52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29656710278332027</v>
+      </c>
+      <c r="O52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.35990513920098877</v>
+      </c>
+      <c r="P52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29102697779771958</v>
+      </c>
+      <c r="Q52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.3679509338588251</v>
+      </c>
+      <c r="R52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.36745727723761246</v>
+      </c>
+      <c r="S52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29736192348070217</v>
+      </c>
+      <c r="T52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29699450030339919</v>
+      </c>
+      <c r="U52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29664256591191041</v>
+      </c>
+      <c r="V52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29744814850239132</v>
+      </c>
+      <c r="W52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.28319238116054807</v>
+      </c>
+      <c r="X52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.3415014650110631</v>
+      </c>
+      <c r="Y52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29962624141612448</v>
+      </c>
+      <c r="Z52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.34704659541983562</v>
+      </c>
+      <c r="AA52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.32250377021174409</v>
+      </c>
+      <c r="AB52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.2835999920971945</v>
+      </c>
+      <c r="AC52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.31748627763471177</v>
+      </c>
+      <c r="AD52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.27856921756054215</v>
+      </c>
+      <c r="AE52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.33662854914990997</v>
+      </c>
+      <c r="AF52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.30288907299400414</v>
+      </c>
+      <c r="AG52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.3299668807799141</v>
+      </c>
+      <c r="AH52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.25867078091215634</v>
+      </c>
+      <c r="AI52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.33230108335523878</v>
+      </c>
+      <c r="AJ52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29589201246673874</v>
+      </c>
+      <c r="AK52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.32118179058848634</v>
+      </c>
+      <c r="AL52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.32112788627248529</v>
+      </c>
+      <c r="AM52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.36126368545297416</v>
+      </c>
+      <c r="AN52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.26068244764233267</v>
+      </c>
+      <c r="AO52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.29284155988315325</v>
+      </c>
+      <c r="AP52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.34180072164729874</v>
+      </c>
+      <c r="AQ52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.33659762497135065</v>
+      </c>
+      <c r="AR52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.33847150623573086</v>
+      </c>
+      <c r="AS52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.35923180463066445</v>
+      </c>
+      <c r="AT52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.32197988371472025</v>
+      </c>
+      <c r="AU52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.34413880752353893</v>
+      </c>
+      <c r="AV52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.36828286383920056</v>
+      </c>
+      <c r="AW52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.32034303530572017</v>
+      </c>
+      <c r="AX52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.28624858158052363</v>
+      </c>
+      <c r="AY52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.3107833176372462</v>
+      </c>
+      <c r="AZ52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.36240354394478724</v>
+      </c>
+      <c r="BA52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.3154421701507763</v>
+      </c>
+      <c r="BB52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.31674362827201519</v>
+      </c>
+      <c r="BC52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.31539067583602354</v>
+      </c>
+      <c r="BD52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.33373350695109216</v>
+      </c>
+      <c r="BE52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.30246143183795865</v>
+      </c>
+      <c r="BF52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.37400200149203694</v>
+      </c>
+      <c r="BG52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.30433013633756079</v>
+      </c>
+      <c r="BH52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.35734558396590077</v>
+      </c>
+      <c r="BI52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.31212966146154186</v>
+      </c>
+      <c r="BJ52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.30135173304737589</v>
+      </c>
+      <c r="BK52" s="33">
+        <f t="shared" si="9"/>
+        <v>0.36388971827823213</v>
       </c>
     </row>
   </sheetData>
@@ -10490,7 +10747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76899784-8E0A-49E5-B47F-56F3E8EDADFC}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -11245,7 +11502,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="29">
         <f>MIN(pypsa!B49:BK49)</f>
@@ -11262,7 +11519,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="29">
         <f>MIN(pypsa!B50:BK50)</f>
@@ -11279,7 +11536,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B51" s="19">
         <f>MIN(pypsa!B51:BK51)</f>
@@ -11296,6 +11553,23 @@
       <c r="E51" s="32">
         <f>MEDIAN(pypsa!B51:BK51)</f>
         <v>0.934480326573353</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="19">
+        <f>MIN(pypsa!B52:BK52)</f>
+        <v>0.25867078091215634</v>
+      </c>
+      <c r="C52" s="20">
+        <f>AVERAGE(pypsa!B52:BK52)</f>
+        <v>0.31950697097857123</v>
+      </c>
+      <c r="D52" s="21">
+        <f>MAX(pypsa!B52:BK52)</f>
+        <v>0.37400200149203694</v>
       </c>
     </row>
   </sheetData>
